--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260820.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260820.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>1,680,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,680,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1751,6 +1751,24 @@
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>RP_NTD</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>7,253,375,044</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
